--- a/xlsx/KV.xlsx
+++ b/xlsx/KV.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5457" uniqueCount="2591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5457" uniqueCount="2592">
   <si>
     <t>SORT</t>
   </si>
@@ -76,7 +76,7 @@
     <t>2 piano pieces</t>
   </si>
   <si>
-    <t>Klavierstücke</t>
+    <t>Klavierstück</t>
   </si>
   <si>
     <t>Piece in G
@@ -6185,21 +6185,21 @@
     <t>2 Flutes, 2 Clarinetts, 2 Bassoons, 2 Violins, Cello, Basso</t>
   </si>
   <si>
+    <t>KV 605</t>
+  </si>
+  <si>
+    <t>3 German Dances</t>
+  </si>
+  <si>
+    <t>No. 3 work of doubtful authenticity</t>
+  </si>
+  <si>
     <t>KV 605,01</t>
   </si>
   <si>
     <t>[German Dances with Trio]</t>
   </si>
   <si>
-    <t>KV 605,01-03</t>
-  </si>
-  <si>
-    <t>3 German Dances</t>
-  </si>
-  <si>
-    <t>No. 3 work of doubtful authenticity</t>
-  </si>
-  <si>
     <t>KV 605,03</t>
   </si>
   <si>
@@ -6608,7 +6608,7 @@
     <t>KV 655</t>
   </si>
   <si>
-    <t>2 Church sonatas in D,  G</t>
+    <t>2 Church Sonatas</t>
   </si>
   <si>
     <t>KV 655/1</t>
@@ -6937,19 +6937,19 @@
     <t>Melodic notation</t>
   </si>
   <si>
+    <t>KV 692</t>
+  </si>
+  <si>
+    <t>2 Masonic Songs</t>
+  </si>
+  <si>
+    <t>prob. Tenor, Male Choir, Piano or Organ</t>
+  </si>
+  <si>
     <t>KV 692,01</t>
   </si>
   <si>
     <t>For the opening of the Masters' lodge "Des Todes Werk"</t>
-  </si>
-  <si>
-    <t>prob. Tenor, Male Choir, Piano or Organ</t>
-  </si>
-  <si>
-    <t>KV 692,01-02</t>
-  </si>
-  <si>
-    <t>2 Masonic Songs</t>
   </si>
   <si>
     <t>KV 692,02</t>
@@ -7159,16 +7159,19 @@
     <t>KV 718</t>
   </si>
   <si>
+    <t>KV 719</t>
+  </si>
+  <si>
+    <t>2 German Dances</t>
+  </si>
+  <si>
+    <t>Werke zweifelhafter Echtheit, fragment</t>
+  </si>
+  <si>
     <t>KV 719,01</t>
   </si>
   <si>
-    <t>KV 719,01-02</t>
-  </si>
-  <si>
-    <t>2 German Dances</t>
-  </si>
-  <si>
-    <t>Werke zweifelhafter Echtheit, fragment</t>
+    <t>German Dance</t>
   </si>
   <si>
     <t>KV 719,02</t>
@@ -9423,10 +9426,11 @@
   <sheetFormatPr defaultColWidth="9.72972972972973" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.4414414414414" style="5" customWidth="1"/>
-    <col min="2" max="2" width="14.4414414414414" style="6" customWidth="1"/>
+    <col min="2" max="2" width="35.7477477477477" style="6" customWidth="1"/>
     <col min="3" max="4" width="14.4414414414414" style="4" customWidth="1"/>
     <col min="5" max="5" width="23.7027027027027" style="3" customWidth="1"/>
-    <col min="6" max="7" width="11.6576576576577" style="5" customWidth="1"/>
+    <col min="6" max="6" width="24.0810810810811" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.6576576576577" style="5" customWidth="1"/>
     <col min="8" max="8" width="23.7027027027027" style="4" customWidth="1"/>
     <col min="9" max="9" width="23.7027027027027" style="3" customWidth="1"/>
     <col min="10" max="10" width="23.7027027027027" style="4" customWidth="1"/>
@@ -9495,7 +9499,7 @@
     </row>
     <row r="3" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="10">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>17</v>
@@ -9519,7 +9523,7 @@
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="10">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>20</v>
@@ -9543,7 +9547,7 @@
     </row>
     <row r="5" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="10">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>22</v>
@@ -9567,7 +9571,7 @@
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A6" s="10">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>24</v>
@@ -9799,7 +9803,7 @@
     </row>
     <row r="15" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A15" s="10">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>50</v>
@@ -9827,7 +9831,7 @@
     </row>
     <row r="16" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A16" s="10">
-        <v>9</v>
+        <v>9.2</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>52</v>
@@ -10056,7 +10060,7 @@
       <c r="B25" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D25" s="17"/>
@@ -11155,7 +11159,7 @@
     </row>
     <row r="68" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A68" s="10">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>136</v>
@@ -11179,7 +11183,7 @@
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A69" s="10">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>138</v>
@@ -11205,7 +11209,7 @@
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A70" s="10">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>142</v>
@@ -11277,7 +11281,7 @@
     </row>
     <row r="73" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A73" s="10">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>153</v>
@@ -11569,7 +11573,7 @@
     </row>
     <row r="85" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A85" s="10">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>183</v>
@@ -11617,7 +11621,7 @@
     </row>
     <row r="87" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A87" s="10">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>189</v>
@@ -11641,7 +11645,7 @@
     </row>
     <row r="88" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A88" s="10">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>193</v>
@@ -11665,7 +11669,7 @@
     </row>
     <row r="89" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A89" s="10">
-        <v>33</v>
+        <v>33.3</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>196</v>
@@ -11691,7 +11695,7 @@
     </row>
     <row r="90" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A90" s="10">
-        <v>33</v>
+        <v>33.4</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>200</v>
@@ -11717,7 +11721,7 @@
     </row>
     <row r="91" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A91" s="10">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>202</v>
@@ -11743,7 +11747,7 @@
     </row>
     <row r="92" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A92" s="10">
-        <v>33</v>
+        <v>33.6</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>204</v>
@@ -11769,7 +11773,7 @@
     </row>
     <row r="93" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A93" s="10">
-        <v>33</v>
+        <v>33.7</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>206</v>
@@ -11795,7 +11799,7 @@
     </row>
     <row r="94" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A94" s="10">
-        <v>33</v>
+        <v>33.8</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>208</v>
@@ -11917,7 +11921,7 @@
     </row>
     <row r="99" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A99" s="10">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>229</v>
@@ -11941,7 +11945,7 @@
     </row>
     <row r="100" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A100" s="10">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>232</v>
@@ -11965,7 +11969,7 @@
     </row>
     <row r="101" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A101" s="10">
-        <v>41</v>
+        <v>41.3</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>236</v>
@@ -11989,7 +11993,7 @@
     </row>
     <row r="102" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A102" s="10">
-        <v>41</v>
+        <v>41.4</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>240</v>
@@ -12011,7 +12015,7 @@
     </row>
     <row r="103" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A103" s="10">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>242</v>
@@ -12037,7 +12041,7 @@
     </row>
     <row r="104" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A104" s="10">
-        <v>41</v>
+        <v>41.6</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>243</v>
@@ -12061,7 +12065,7 @@
     </row>
     <row r="105" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A105" s="10">
-        <v>41</v>
+        <v>41.7</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>245</v>
@@ -12135,7 +12139,7 @@
     </row>
     <row r="108" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A108" s="10">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>255</v>
@@ -12183,7 +12187,7 @@
     </row>
     <row r="110" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A110" s="10">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>262</v>
@@ -12207,7 +12211,7 @@
     </row>
     <row r="111" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A111" s="10">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="B111" s="11" t="s">
         <v>264</v>
@@ -12233,7 +12237,7 @@
     </row>
     <row r="112" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A112" s="10">
-        <v>46</v>
+        <v>45.4</v>
       </c>
       <c r="B112" s="11" t="s">
         <v>266</v>
@@ -12257,7 +12261,7 @@
     </row>
     <row r="113" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A113" s="10">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>268</v>
@@ -12307,7 +12311,7 @@
     </row>
     <row r="115" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A115" s="10">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>274</v>
@@ -12333,7 +12337,7 @@
     </row>
     <row r="116" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A116" s="10">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>276</v>
@@ -12607,7 +12611,7 @@
     </row>
     <row r="127" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A127" s="10">
-        <v>65</v>
+        <v>65.1</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>315</v>
@@ -12655,7 +12659,7 @@
     </row>
     <row r="129" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A129" s="10">
-        <v>66</v>
+        <v>66.3</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>322</v>
@@ -12681,7 +12685,7 @@
     </row>
     <row r="130" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A130" s="10">
-        <v>66</v>
+        <v>66.4</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>324</v>
@@ -12707,7 +12711,7 @@
     </row>
     <row r="131" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A131" s="10">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>326</v>
@@ -12893,7 +12897,7 @@
     </row>
     <row r="138" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A138" s="10">
-        <v>72</v>
+        <v>72.1</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>350</v>
@@ -12921,7 +12925,7 @@
     </row>
     <row r="139" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A139" s="10">
-        <v>72</v>
+        <v>72.2</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>354</v>
@@ -12971,7 +12975,7 @@
     </row>
     <row r="141" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A141" s="10">
-        <v>73</v>
+        <v>73.4</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>360</v>
@@ -13021,7 +13025,7 @@
     </row>
     <row r="143" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A143" s="10">
-        <v>74</v>
+        <v>74.2</v>
       </c>
       <c r="B143" s="11" t="s">
         <v>364</v>
@@ -13047,7 +13051,7 @@
     </row>
     <row r="144" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A144" s="10">
-        <v>74</v>
+        <v>74.7</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>367</v>
@@ -14973,7 +14977,7 @@
     </row>
     <row r="222" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A222" s="10">
-        <v>168</v>
+        <v>168.1</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>595</v>
@@ -28058,36 +28062,36 @@
       <c r="F740" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G740" s="10" t="s">
-        <v>41</v>
-      </c>
+      <c r="G740" s="10"/>
       <c r="H740" s="12"/>
-      <c r="I740" s="13"/>
-      <c r="J740" s="13"/>
+      <c r="I740" s="13" t="s">
+        <v>1920</v>
+      </c>
+      <c r="J740" s="13" t="s">
+        <v>1938</v>
+      </c>
     </row>
     <row r="741" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A741" s="10">
         <v>605</v>
       </c>
       <c r="B741" s="11" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="C741" s="12"/>
       <c r="D741" s="12"/>
       <c r="E741" s="13" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="F741" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G741" s="10"/>
+      <c r="G741" s="10" t="s">
+        <v>41</v>
+      </c>
       <c r="H741" s="12"/>
-      <c r="I741" s="13" t="s">
-        <v>1920</v>
-      </c>
-      <c r="J741" s="13" t="s">
-        <v>1940</v>
-      </c>
+      <c r="I741" s="13"/>
+      <c r="J741" s="13"/>
     </row>
     <row r="742" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A742" s="10">
@@ -29515,7 +29519,7 @@
     </row>
     <row r="798" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A798" s="10">
-        <v>655</v>
+        <v>655.1</v>
       </c>
       <c r="B798" s="11" t="s">
         <v>2078</v>
@@ -29541,7 +29545,7 @@
     </row>
     <row r="799" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A799" s="10">
-        <v>655</v>
+        <v>655.2</v>
       </c>
       <c r="B799" s="11" t="s">
         <v>2080</v>
@@ -31261,20 +31265,18 @@
       </c>
       <c r="D866" s="17"/>
       <c r="E866" s="13" t="s">
-        <v>1942</v>
+        <v>2257</v>
       </c>
       <c r="F866" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G866" s="10" t="s">
-        <v>366</v>
-      </c>
+      <c r="G866" s="10"/>
       <c r="H866" s="12"/>
       <c r="I866" s="13" t="s">
         <v>319</v>
       </c>
       <c r="J866" s="13" t="s">
-        <v>2086</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="867" s="2" customFormat="1" customHeight="1" spans="1:10">
@@ -31282,25 +31284,27 @@
         <v>719</v>
       </c>
       <c r="B867" s="11" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="C867" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D867" s="17"/>
       <c r="E867" s="13" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="F867" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="G867" s="10"/>
+      <c r="G867" s="10" t="s">
+        <v>366</v>
+      </c>
       <c r="H867" s="12"/>
       <c r="I867" s="13" t="s">
         <v>319</v>
       </c>
       <c r="J867" s="13" t="s">
-        <v>2259</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="868" s="4" customFormat="1" customHeight="1" spans="1:10">
@@ -31308,14 +31312,14 @@
         <v>719</v>
       </c>
       <c r="B868" s="11" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="C868" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D868" s="17"/>
       <c r="E868" s="13" t="s">
-        <v>1942</v>
+        <v>2260</v>
       </c>
       <c r="F868" s="10" t="s">
         <v>318</v>
@@ -31336,10 +31340,10 @@
         <v>720</v>
       </c>
       <c r="B869" s="11" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="C869" s="12" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="D869" s="12"/>
       <c r="E869" s="13" t="s">
@@ -31358,14 +31362,14 @@
         <v>721</v>
       </c>
       <c r="B870" s="11" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="C870" s="12" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="D870" s="12"/>
       <c r="E870" s="13" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="F870" s="10"/>
       <c r="G870" s="10"/>
@@ -31379,13 +31383,13 @@
     </row>
     <row r="871" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A871" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B871" s="11" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="C871" s="12" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="D871" s="12"/>
       <c r="E871" s="13"/>
@@ -31395,19 +31399,19 @@
       <c r="G871" s="10"/>
       <c r="H871" s="12"/>
       <c r="I871" s="13" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="J871" s="12"/>
     </row>
     <row r="872" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A872" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B872" s="11" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="C872" s="12" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="D872" s="12"/>
       <c r="E872" s="13"/>
@@ -31417,25 +31421,25 @@
       <c r="G872" s="10"/>
       <c r="H872" s="12"/>
       <c r="I872" s="13" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="J872" s="12" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="873" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A873" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B873" s="11" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="C873" s="12" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="D873" s="12"/>
       <c r="E873" s="13" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="F873" s="10" t="s">
         <v>277</v>
@@ -31447,13 +31451,13 @@
     </row>
     <row r="874" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A874" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B874" s="11" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="C874" s="12" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="D874" s="12"/>
       <c r="E874" s="13"/>
@@ -31465,21 +31469,21 @@
       </c>
       <c r="H874" s="12"/>
       <c r="I874" s="13" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="J874" s="12" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="875" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A875" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B875" s="11" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="C875" s="12" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="D875" s="12"/>
       <c r="E875" s="13"/>
@@ -31489,19 +31493,19 @@
       <c r="G875" s="10"/>
       <c r="H875" s="12"/>
       <c r="I875" s="13" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="J875" s="12"/>
     </row>
     <row r="876" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A876" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B876" s="11" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="C876" s="12" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="D876" s="12"/>
       <c r="E876" s="13"/>
@@ -31513,19 +31517,19 @@
       </c>
       <c r="H876" s="12"/>
       <c r="I876" s="13" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="J876" s="12"/>
     </row>
     <row r="877" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A877" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B877" s="11" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="C877" s="12" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="D877" s="12"/>
       <c r="E877" s="13"/>
@@ -31535,19 +31539,19 @@
       <c r="G877" s="10"/>
       <c r="H877" s="12"/>
       <c r="I877" s="13" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="J877" s="12"/>
     </row>
     <row r="878" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A878" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B878" s="11" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="C878" s="12" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="D878" s="12"/>
       <c r="E878" s="13" t="s">
@@ -31559,23 +31563,23 @@
       <c r="G878" s="10"/>
       <c r="H878" s="12"/>
       <c r="I878" s="13" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="J878" s="12"/>
     </row>
     <row r="879" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A879" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B879" s="11" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="C879" s="12" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="D879" s="12"/>
       <c r="E879" s="13" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="F879" s="10" t="s">
         <v>277</v>
@@ -31583,23 +31587,23 @@
       <c r="G879" s="10"/>
       <c r="H879" s="12"/>
       <c r="I879" s="13" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="J879" s="12"/>
     </row>
     <row r="880" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A880" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B880" s="11" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="C880" s="12" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="D880" s="12"/>
       <c r="E880" s="13" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="F880" s="10" t="s">
         <v>277</v>
@@ -31611,17 +31615,17 @@
     </row>
     <row r="881" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A881" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B881" s="11" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="C881" s="12" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="D881" s="12"/>
       <c r="E881" s="13" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="F881" s="10" t="s">
         <v>277</v>
@@ -31633,17 +31637,17 @@
     </row>
     <row r="882" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A882" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B882" s="11" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="C882" s="12" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="D882" s="12"/>
       <c r="E882" s="13" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="F882" s="10" t="s">
         <v>277</v>
@@ -31655,17 +31659,17 @@
     </row>
     <row r="883" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A883" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B883" s="11" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="C883" s="12" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="D883" s="12"/>
       <c r="E883" s="13" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="F883" s="10" t="s">
         <v>277</v>
@@ -31673,23 +31677,23 @@
       <c r="G883" s="10"/>
       <c r="H883" s="12"/>
       <c r="I883" s="13" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="J883" s="12"/>
     </row>
     <row r="884" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A884" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B884" s="11" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="C884" s="12" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="D884" s="12"/>
       <c r="E884" s="13" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="F884" s="10" t="s">
         <v>277</v>
@@ -31698,20 +31702,20 @@
       <c r="H884" s="12"/>
       <c r="I884" s="13"/>
       <c r="J884" s="12" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="885" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A885" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B885" s="11" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="C885" s="12"/>
       <c r="D885" s="12"/>
       <c r="E885" s="13" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="F885" s="10" t="s">
         <v>277</v>
@@ -31727,17 +31731,17 @@
     </row>
     <row r="886" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A886" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B886" s="11" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="C886" s="12" t="s">
         <v>25</v>
       </c>
       <c r="D886" s="12"/>
       <c r="E886" s="13" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="F886" s="10" t="s">
         <v>277</v>
@@ -31745,23 +31749,23 @@
       <c r="G886" s="10"/>
       <c r="H886" s="12"/>
       <c r="I886" s="13" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="J886" s="12"/>
     </row>
     <row r="887" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A887" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B887" s="11" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="C887" s="12" t="s">
         <v>25</v>
       </c>
       <c r="D887" s="12"/>
       <c r="E887" s="13" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="F887" s="10" t="s">
         <v>277</v>
@@ -31775,65 +31779,65 @@
     </row>
     <row r="888" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A888" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B888" s="11" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="C888" s="12" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="D888" s="12"/>
       <c r="E888" s="13" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="F888" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G888" s="10"/>
       <c r="H888" s="12"/>
       <c r="I888" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J888" s="12"/>
     </row>
     <row r="889" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A889" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B889" s="11" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="C889" s="12"/>
       <c r="D889" s="12"/>
       <c r="E889" s="13" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="F889" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G889" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H889" s="12"/>
       <c r="I889" s="13" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="J889" s="12"/>
     </row>
     <row r="890" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A890" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B890" s="11" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="C890" s="12" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="D890" s="12"/>
       <c r="E890" s="13" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="F890" s="10"/>
       <c r="G890" s="10" t="s">
@@ -31841,19 +31845,19 @@
       </c>
       <c r="H890" s="12"/>
       <c r="I890" s="13" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="J890" s="12"/>
     </row>
     <row r="891" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A891" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B891" s="11" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="C891" s="12" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="D891" s="12"/>
       <c r="E891" s="13"/>
@@ -31865,21 +31869,21 @@
       </c>
       <c r="H891" s="12"/>
       <c r="I891" s="13" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="J891" s="12" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="892" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A892" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B892" s="11" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="C892" s="12" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="D892" s="12"/>
       <c r="E892" s="13"/>
@@ -31891,21 +31895,21 @@
       </c>
       <c r="H892" s="12"/>
       <c r="I892" s="13" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="J892" s="12" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="893" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A893" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B893" s="11" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="C893" s="12" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="D893" s="12"/>
       <c r="E893" s="13"/>
@@ -31917,18 +31921,18 @@
       </c>
       <c r="H893" s="12"/>
       <c r="I893" s="13" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="J893" s="12" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="894" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A894" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B894" s="11" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="C894" s="12"/>
       <c r="D894" s="12"/>
@@ -31944,15 +31948,15 @@
       <c r="H894" s="12"/>
       <c r="I894" s="13"/>
       <c r="J894" s="12" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="895" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A895" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B895" s="11" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="C895" s="12" t="s">
         <v>25</v>
@@ -31967,18 +31971,18 @@
       </c>
       <c r="H895" s="12"/>
       <c r="I895" s="13" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="J895" s="12" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="896" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A896" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B896" s="11" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="C896" s="12" t="s">
         <v>25</v>
@@ -31993,18 +31997,18 @@
       </c>
       <c r="H896" s="12"/>
       <c r="I896" s="13" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="J896" s="12" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="897" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A897" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B897" s="11" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="C897" s="12" t="s">
         <v>25</v>
@@ -32019,18 +32023,18 @@
       </c>
       <c r="H897" s="12"/>
       <c r="I897" s="13" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="J897" s="12" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="898" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A898" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B898" s="11" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="C898" s="12" t="s">
         <v>25</v>
@@ -32045,47 +32049,47 @@
       </c>
       <c r="H898" s="12"/>
       <c r="I898" s="13" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="J898" s="12" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="899" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A899" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B899" s="11" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="C899" s="12" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="D899" s="12"/>
       <c r="E899" s="13" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="F899" s="10"/>
       <c r="G899" s="10"/>
       <c r="H899" s="12"/>
       <c r="I899" s="13" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="J899" s="12" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="900" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A900" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B900" s="11" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="C900" s="12"/>
       <c r="D900" s="12"/>
       <c r="E900" s="13" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="F900" s="10" t="s">
         <v>387</v>
@@ -32097,17 +32101,17 @@
     </row>
     <row r="901" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A901" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B901" s="11" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="C901" s="12" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="D901" s="12"/>
       <c r="E901" s="13" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="F901" s="10" t="s">
         <v>387</v>
@@ -32115,23 +32119,23 @@
       <c r="G901" s="10"/>
       <c r="H901" s="12"/>
       <c r="I901" s="13" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="J901" s="12"/>
     </row>
     <row r="902" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A902" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B902" s="11" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="C902" s="12" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="D902" s="12"/>
       <c r="E902" s="13" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="F902" s="10" t="s">
         <v>387</v>
@@ -32139,23 +32143,23 @@
       <c r="G902" s="10"/>
       <c r="H902" s="12"/>
       <c r="I902" s="13" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="J902" s="12"/>
     </row>
     <row r="903" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A903" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B903" s="11" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="C903" s="12" t="s">
         <v>25</v>
       </c>
       <c r="D903" s="12"/>
       <c r="E903" s="13" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="F903" s="10" t="s">
         <v>387</v>
@@ -32163,21 +32167,21 @@
       <c r="G903" s="10"/>
       <c r="H903" s="12"/>
       <c r="I903" s="13" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="J903" s="12"/>
     </row>
     <row r="904" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A904" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B904" s="11" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="C904" s="12"/>
       <c r="D904" s="12"/>
       <c r="E904" s="13" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="F904" s="10" t="s">
         <v>387</v>
@@ -32185,67 +32189,67 @@
       <c r="G904" s="10"/>
       <c r="H904" s="12"/>
       <c r="I904" s="13" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="J904" s="12"/>
     </row>
     <row r="905" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A905" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B905" s="11" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="C905" s="12" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="D905" s="12"/>
       <c r="E905" s="13" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="F905" s="10"/>
       <c r="G905" s="10"/>
       <c r="H905" s="12"/>
       <c r="I905" s="13" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="J905" s="12"/>
     </row>
     <row r="906" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A906" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B906" s="11" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="C906" s="12" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="D906" s="12"/>
       <c r="E906" s="13" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="F906" s="10"/>
       <c r="G906" s="10"/>
       <c r="H906" s="12"/>
       <c r="I906" s="13" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="J906" s="12"/>
     </row>
     <row r="907" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A907" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B907" s="11" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="C907" s="12" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="D907" s="12"/>
       <c r="E907" s="13" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="F907" s="10" t="s">
         <v>1423</v>
@@ -32257,13 +32261,13 @@
     </row>
     <row r="908" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A908" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B908" s="11" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="C908" s="12" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="D908" s="12"/>
       <c r="E908" s="13"/>
@@ -32276,15 +32280,15 @@
       <c r="H908" s="12"/>
       <c r="I908" s="13"/>
       <c r="J908" s="12" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="909" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A909" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B909" s="11" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="C909" s="12"/>
       <c r="D909" s="12"/>
@@ -32296,18 +32300,18 @@
       <c r="H909" s="12"/>
       <c r="I909" s="13"/>
       <c r="J909" s="12" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="910" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A910" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B910" s="11" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="C910" s="12" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="D910" s="12"/>
       <c r="E910" s="13"/>
@@ -32317,25 +32321,25 @@
       <c r="G910" s="10"/>
       <c r="H910" s="12"/>
       <c r="I910" s="13" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J910" s="12" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="911" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A911" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B911" s="11" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="C911" s="12" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="D911" s="12"/>
       <c r="E911" s="13" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="F911" s="10" t="s">
         <v>36</v>
@@ -32347,13 +32351,13 @@
     </row>
     <row r="912" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A912" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B912" s="11" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="C912" s="12" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="D912" s="12"/>
       <c r="E912" s="13"/>
@@ -32365,21 +32369,21 @@
       </c>
       <c r="H912" s="12"/>
       <c r="I912" s="13" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J912" s="12" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="913" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A913" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B913" s="11" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="C913" s="12" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="D913" s="12"/>
       <c r="E913" s="13"/>
@@ -32389,21 +32393,21 @@
       <c r="G913" s="10"/>
       <c r="H913" s="12"/>
       <c r="I913" s="13" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J913" s="12" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="914" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A914" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B914" s="11" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="C914" s="12" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="D914" s="12"/>
       <c r="E914" s="13"/>
@@ -32415,21 +32419,21 @@
       </c>
       <c r="H914" s="12"/>
       <c r="I914" s="13" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J914" s="12" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="915" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A915" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B915" s="11" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="C915" s="12" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="D915" s="12"/>
       <c r="E915" s="13"/>
@@ -32441,21 +32445,21 @@
       </c>
       <c r="H915" s="12"/>
       <c r="I915" s="13" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J915" s="12" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="916" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A916" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B916" s="11" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="C916" s="12" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="D916" s="12"/>
       <c r="E916" s="13"/>
@@ -32467,21 +32471,21 @@
       </c>
       <c r="H916" s="12"/>
       <c r="I916" s="13" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="J916" s="12" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="917" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A917" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B917" s="11" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="C917" s="12" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="D917" s="12"/>
       <c r="E917" s="13"/>
@@ -32494,18 +32498,18 @@
       <c r="H917" s="12"/>
       <c r="I917" s="13"/>
       <c r="J917" s="12" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="918" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A918" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B918" s="11" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C918" s="12" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="D918" s="12"/>
       <c r="E918" s="13"/>
@@ -32521,13 +32525,13 @@
     </row>
     <row r="919" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A919" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B919" s="11" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="C919" s="12" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="D919" s="12"/>
       <c r="E919" s="13"/>
@@ -32539,23 +32543,23 @@
       </c>
       <c r="H919" s="12"/>
       <c r="I919" s="13" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="J919" s="12"/>
     </row>
     <row r="920" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A920" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B920" s="11" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="C920" s="12" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="D920" s="12"/>
       <c r="E920" s="13" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="F920" s="10" t="s">
         <v>13</v>
@@ -32569,13 +32573,13 @@
     </row>
     <row r="921" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A921" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B921" s="11" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="C921" s="12" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="D921" s="12"/>
       <c r="E921" s="13"/>
@@ -32587,21 +32591,21 @@
       </c>
       <c r="H921" s="12"/>
       <c r="I921" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J921" s="12" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="922" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A922" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B922" s="11" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="C922" s="12" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D922" s="12"/>
       <c r="E922" s="13"/>
@@ -32613,23 +32617,23 @@
       </c>
       <c r="H922" s="12"/>
       <c r="I922" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J922" s="12"/>
     </row>
     <row r="923" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A923" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B923" s="11" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="C923" s="12" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D923" s="12"/>
       <c r="E923" s="13" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="F923" s="10" t="s">
         <v>156</v>
@@ -32639,26 +32643,26 @@
       </c>
       <c r="H923" s="12"/>
       <c r="I923" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J923" s="12"/>
     </row>
     <row r="924" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A924" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B924" s="11" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="C924" s="12" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="D924" s="12"/>
       <c r="E924" s="13" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="F924" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G924" s="10"/>
       <c r="H924" s="12"/>
@@ -32667,18 +32671,18 @@
     </row>
     <row r="925" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A925" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B925" s="11" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="C925" s="12"/>
       <c r="D925" s="12"/>
       <c r="E925" s="13" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="F925" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G925" s="10" t="s">
         <v>77</v>
@@ -32686,25 +32690,25 @@
       <c r="H925" s="12"/>
       <c r="I925" s="13"/>
       <c r="J925" s="12" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="926" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A926" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B926" s="11" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="C926" s="12" t="s">
         <v>2163</v>
       </c>
       <c r="D926" s="12"/>
       <c r="E926" s="13" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="F926" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G926" s="10"/>
       <c r="H926" s="12"/>
@@ -32715,18 +32719,18 @@
     </row>
     <row r="927" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A927" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B927" s="11" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="C927" s="12"/>
       <c r="D927" s="12"/>
       <c r="E927" s="13" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="F927" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G927" s="10"/>
       <c r="H927" s="12"/>
@@ -32735,18 +32739,18 @@
     </row>
     <row r="928" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A928" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B928" s="11" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="C928" s="12"/>
       <c r="D928" s="12"/>
       <c r="E928" s="13" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="F928" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G928" s="10"/>
       <c r="H928" s="12"/>
@@ -32755,18 +32759,18 @@
     </row>
     <row r="929" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A929" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B929" s="11" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="C929" s="12"/>
       <c r="D929" s="12"/>
       <c r="E929" s="13" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="F929" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G929" s="10" t="s">
         <v>77</v>
@@ -32777,18 +32781,18 @@
     </row>
     <row r="930" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A930" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B930" s="11" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="C930" s="12"/>
       <c r="D930" s="12"/>
       <c r="E930" s="13" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="F930" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G930" s="10" t="s">
         <v>30</v>
@@ -32799,44 +32803,44 @@
     </row>
     <row r="931" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A931" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B931" s="11" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="C931" s="12" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="D931" s="12"/>
       <c r="E931" s="13" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="F931" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G931" s="10"/>
       <c r="H931" s="12"/>
       <c r="I931" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J931" s="12" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="932" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A932" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B932" s="11" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="C932" s="12"/>
       <c r="D932" s="12"/>
       <c r="E932" s="13" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="F932" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G932" s="10"/>
       <c r="H932" s="12"/>
@@ -32845,142 +32849,142 @@
     </row>
     <row r="933" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A933" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B933" s="11" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="C933" s="12" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="D933" s="12"/>
       <c r="E933" s="13" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="F933" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G933" s="10"/>
       <c r="H933" s="12"/>
       <c r="I933" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J933" s="12"/>
     </row>
     <row r="934" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A934" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B934" s="11" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="C934" s="12" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="D934" s="12"/>
       <c r="E934" s="13" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="F934" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G934" s="10"/>
       <c r="H934" s="12"/>
       <c r="I934" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J934" s="12" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="935" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A935" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B935" s="11" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="C935" s="12" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="D935" s="12"/>
       <c r="E935" s="13" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="F935" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G935" s="10"/>
       <c r="H935" s="12"/>
       <c r="I935" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J935" s="12"/>
     </row>
     <row r="936" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A936" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B936" s="11" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="C936" s="12" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="D936" s="12"/>
       <c r="E936" s="13" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="F936" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G936" s="10"/>
       <c r="H936" s="12"/>
       <c r="I936" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J936" s="12"/>
     </row>
     <row r="937" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A937" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B937" s="11" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="C937" s="12" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="D937" s="12"/>
       <c r="E937" s="13" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="F937" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G937" s="10"/>
       <c r="H937" s="12"/>
       <c r="I937" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J937" s="12" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="938" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A938" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B938" s="11" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="C938" s="12"/>
       <c r="D938" s="12"/>
       <c r="E938" s="13" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="F938" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G938" s="10"/>
       <c r="H938" s="12"/>
@@ -32989,18 +32993,18 @@
     </row>
     <row r="939" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A939" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B939" s="11" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="C939" s="12"/>
       <c r="D939" s="12"/>
       <c r="E939" s="13" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="F939" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G939" s="10"/>
       <c r="H939" s="12"/>
@@ -33011,18 +33015,18 @@
     </row>
     <row r="940" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A940" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B940" s="11" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="C940" s="12"/>
       <c r="D940" s="12"/>
       <c r="E940" s="13" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="F940" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G940" s="10" t="s">
         <v>30</v>
@@ -33035,18 +33039,18 @@
     </row>
     <row r="941" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A941" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B941" s="11" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="C941" s="12"/>
       <c r="D941" s="12"/>
       <c r="E941" s="13" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="F941" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G941" s="10" t="s">
         <v>23</v>
@@ -33057,20 +33061,20 @@
     </row>
     <row r="942" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A942" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B942" s="11" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="C942" s="12" t="s">
         <v>2163</v>
       </c>
       <c r="D942" s="12"/>
       <c r="E942" s="13" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="F942" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G942" s="10" t="s">
         <v>89</v>
@@ -33083,20 +33087,20 @@
     </row>
     <row r="943" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A943" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B943" s="11" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="C943" s="12" t="s">
         <v>2163</v>
       </c>
       <c r="D943" s="12"/>
       <c r="E943" s="13" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="F943" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G943" s="10" t="s">
         <v>19</v>
@@ -33109,72 +33113,72 @@
     </row>
     <row r="944" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A944" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B944" s="11" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="C944" s="12" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="D944" s="12"/>
       <c r="E944" s="13" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="F944" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G944" s="10" t="s">
         <v>62</v>
       </c>
       <c r="H944" s="12"/>
       <c r="I944" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J944" s="12"/>
     </row>
     <row r="945" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A945" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B945" s="11" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="C945" s="12" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="D945" s="12"/>
       <c r="E945" s="13" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="F945" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G945" s="10" t="s">
         <v>19</v>
       </c>
       <c r="H945" s="12"/>
       <c r="I945" s="13" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="J945" s="12"/>
     </row>
     <row r="946" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A946" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B946" s="11" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="C946" s="12" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="D946" s="12"/>
       <c r="E946" s="13" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="F946" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G946" s="10"/>
       <c r="H946" s="12"/>
@@ -33183,20 +33187,20 @@
     </row>
     <row r="947" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A947" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B947" s="11" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="C947" s="12" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="D947" s="12"/>
       <c r="E947" s="13" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="F947" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G947" s="10"/>
       <c r="H947" s="12"/>
@@ -33205,20 +33209,20 @@
     </row>
     <row r="948" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A948" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B948" s="11" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="C948" s="12" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="D948" s="12"/>
       <c r="E948" s="13" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="F948" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G948" s="10"/>
       <c r="H948" s="12"/>
@@ -33227,20 +33231,20 @@
     </row>
     <row r="949" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A949" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B949" s="11" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="C949" s="12" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="D949" s="12"/>
       <c r="E949" s="13" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="F949" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G949" s="10" t="s">
         <v>23</v>
@@ -33251,18 +33255,18 @@
     </row>
     <row r="950" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A950" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B950" s="11" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="C950" s="12"/>
       <c r="D950" s="12"/>
       <c r="E950" s="13" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="F950" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G950" s="10" t="s">
         <v>30</v>
@@ -33273,20 +33277,20 @@
     </row>
     <row r="951" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A951" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B951" s="11" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="C951" s="12" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="D951" s="12"/>
       <c r="E951" s="13" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="F951" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G951" s="10" t="s">
         <v>41</v>
@@ -33297,20 +33301,20 @@
     </row>
     <row r="952" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A952" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B952" s="11" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="C952" s="12" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="D952" s="12"/>
       <c r="E952" s="13" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="F952" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G952" s="10"/>
       <c r="H952" s="12"/>
@@ -33319,46 +33323,46 @@
     </row>
     <row r="953" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A953" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B953" s="11" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="C953" s="12" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="D953" s="12"/>
       <c r="E953" s="13" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="F953" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G953" s="10" t="s">
         <v>41</v>
       </c>
       <c r="H953" s="12"/>
       <c r="I953" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J953" s="12"/>
     </row>
     <row r="954" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A954" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B954" s="11" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="C954" s="12" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="D954" s="12"/>
       <c r="E954" s="13" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="F954" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G954" s="10"/>
       <c r="H954" s="12"/>
@@ -33367,44 +33371,44 @@
     </row>
     <row r="955" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A955" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B955" s="11" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="C955" s="12" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="D955" s="12"/>
       <c r="E955" s="13" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="F955" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G955" s="10"/>
       <c r="H955" s="12"/>
       <c r="I955" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J955" s="12"/>
     </row>
     <row r="956" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A956" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B956" s="11" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="C956" s="12" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="D956" s="12"/>
       <c r="E956" s="13" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="F956" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G956" s="10" t="s">
         <v>41</v>
@@ -33419,44 +33423,44 @@
     </row>
     <row r="957" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A957" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B957" s="11" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="C957" s="12" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="D957" s="12"/>
       <c r="E957" s="13" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="F957" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G957" s="10"/>
       <c r="H957" s="12"/>
       <c r="I957" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J957" s="12"/>
     </row>
     <row r="958" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A958" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B958" s="11" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="C958" s="12" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D958" s="12"/>
       <c r="E958" s="13" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="F958" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G958" s="10" t="s">
         <v>77</v>
@@ -33467,20 +33471,20 @@
     </row>
     <row r="959" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A959" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B959" s="11" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="C959" s="12" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D959" s="12"/>
       <c r="E959" s="13" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="F959" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G959" s="10" t="s">
         <v>77</v>
@@ -33491,20 +33495,20 @@
     </row>
     <row r="960" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A960" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B960" s="11" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="C960" s="12" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D960" s="12"/>
       <c r="E960" s="13" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="F960" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G960" s="10" t="s">
         <v>77</v>
@@ -33515,20 +33519,20 @@
     </row>
     <row r="961" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A961" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B961" s="11" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="C961" s="12" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="D961" s="12"/>
       <c r="E961" s="13" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="F961" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G961" s="10" t="s">
         <v>77</v>
@@ -33539,73 +33543,73 @@
     </row>
     <row r="962" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A962" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B962" s="11" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="C962" s="12" t="s">
         <v>2163</v>
       </c>
       <c r="D962" s="12"/>
       <c r="E962" s="13" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="F962" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G962" s="10"/>
       <c r="H962" s="12"/>
       <c r="I962" s="13"/>
       <c r="J962" s="12" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="963" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A963" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B963" s="11" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="C963" s="12" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="D963" s="12"/>
       <c r="E963" s="13" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="F963" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G963" s="10"/>
       <c r="H963" s="12"/>
       <c r="I963" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J963" s="12"/>
     </row>
     <row r="964" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A964" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B964" s="11" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="C964" s="12" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="D964" s="12"/>
       <c r="E964" s="13" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="F964" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G964" s="10"/>
       <c r="H964" s="12"/>
       <c r="I964" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J964" s="12" t="s">
         <v>444</v>
@@ -33613,92 +33617,92 @@
     </row>
     <row r="965" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A965" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B965" s="11" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="C965" s="12" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="D965" s="12"/>
       <c r="E965" s="13" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="F965" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G965" s="10"/>
       <c r="H965" s="12"/>
       <c r="I965" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J965" s="12"/>
     </row>
     <row r="966" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A966" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B966" s="11" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="C966" s="12" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="D966" s="12"/>
       <c r="E966" s="13" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="F966" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G966" s="10"/>
       <c r="H966" s="12"/>
       <c r="I966" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J966" s="12"/>
     </row>
     <row r="967" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A967" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B967" s="11" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="C967" s="15" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="D967" s="15"/>
       <c r="E967" s="12" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="F967" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G967" s="10"/>
       <c r="H967" s="12"/>
       <c r="I967" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J967" s="12"/>
     </row>
     <row r="968" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A968" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B968" s="11" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C968" s="12" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="D968" s="12"/>
       <c r="E968" s="13" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="F968" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G968" s="10" t="s">
         <v>30</v>
@@ -33709,20 +33713,20 @@
     </row>
     <row r="969" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A969" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B969" s="11" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="C969" s="12" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="D969" s="12"/>
       <c r="E969" s="13" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="F969" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G969" s="10" t="s">
         <v>30</v>
@@ -33733,96 +33737,96 @@
     </row>
     <row r="970" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A970" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B970" s="11" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="C970" s="12" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="D970" s="12"/>
       <c r="E970" s="13" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="F970" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G970" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H970" s="12"/>
       <c r="I970" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J970" s="12"/>
     </row>
     <row r="971" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A971" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B971" s="11" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C971" s="12" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="D971" s="12"/>
       <c r="E971" s="13" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="F971" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G971" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H971" s="12"/>
       <c r="I971" s="13" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="J971" s="12"/>
     </row>
     <row r="972" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A972" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B972" s="11" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="C972" s="12" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="D972" s="12"/>
       <c r="E972" s="13" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="F972" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G972" s="10"/>
       <c r="H972" s="12"/>
       <c r="I972" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J972" s="12"/>
     </row>
     <row r="973" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A973" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B973" s="11" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="C973" s="12" t="s">
         <v>2163</v>
       </c>
       <c r="D973" s="12"/>
       <c r="E973" s="13" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="F973" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G973" s="10"/>
       <c r="H973" s="12"/>
@@ -33831,20 +33835,20 @@
     </row>
     <row r="974" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A974" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B974" s="11" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="C974" s="12" t="s">
         <v>2163</v>
       </c>
       <c r="D974" s="12"/>
       <c r="E974" s="13" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="F974" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G974" s="10"/>
       <c r="H974" s="12"/>
@@ -33853,266 +33857,266 @@
     </row>
     <row r="975" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A975" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B975" s="11" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="C975" s="12" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="D975" s="12"/>
       <c r="E975" s="13" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="F975" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G975" s="10"/>
       <c r="H975" s="12"/>
       <c r="I975" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J975" s="12"/>
     </row>
     <row r="976" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A976" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B976" s="11" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="C976" s="12" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="D976" s="12"/>
       <c r="E976" s="13" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="F976" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G976" s="10"/>
       <c r="H976" s="12"/>
       <c r="I976" s="13" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="J976" s="12"/>
     </row>
     <row r="977" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A977" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B977" s="11" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="C977" s="12" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="D977" s="12"/>
       <c r="E977" s="13" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="F977" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G977" s="10"/>
       <c r="H977" s="12"/>
       <c r="I977" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J977" s="12"/>
     </row>
     <row r="978" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A978" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B978" s="11" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="C978" s="12" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="D978" s="12"/>
       <c r="E978" s="13" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="F978" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G978" s="10"/>
       <c r="H978" s="12"/>
       <c r="I978" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J978" s="12"/>
     </row>
     <row r="979" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A979" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B979" s="11" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="C979" s="12" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="D979" s="12"/>
       <c r="E979" s="13" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="F979" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G979" s="10"/>
       <c r="H979" s="12"/>
       <c r="I979" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J979" s="12"/>
     </row>
     <row r="980" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A980" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B980" s="11" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="C980" s="12" t="s">
         <v>2163</v>
       </c>
       <c r="D980" s="12"/>
       <c r="E980" s="13" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="F980" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G980" s="10"/>
       <c r="H980" s="12"/>
       <c r="I980" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J980" s="12"/>
     </row>
     <row r="981" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A981" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B981" s="11" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="C981" s="12" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="D981" s="12"/>
       <c r="E981" s="13" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="F981" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G981" s="10" t="s">
         <v>30</v>
       </c>
       <c r="H981" s="12"/>
       <c r="I981" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J981" s="12"/>
     </row>
     <row r="982" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A982" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B982" s="11" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="C982" s="12" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="D982" s="12"/>
       <c r="E982" s="13" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="F982" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G982" s="10" t="s">
         <v>23</v>
       </c>
       <c r="H982" s="12"/>
       <c r="I982" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J982" s="12"/>
     </row>
     <row r="983" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A983" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B983" s="11" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="C983" s="12" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="D983" s="12"/>
       <c r="E983" s="13" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="F983" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G983" s="10" t="s">
         <v>23</v>
       </c>
       <c r="H983" s="12"/>
       <c r="I983" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J983" s="12"/>
     </row>
     <row r="984" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A984" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B984" s="11" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="C984" s="12" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="D984" s="12"/>
       <c r="E984" s="13" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="F984" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G984" s="10" t="s">
         <v>23</v>
       </c>
       <c r="H984" s="12"/>
       <c r="I984" s="13" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="J984" s="12"/>
     </row>
     <row r="985" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A985" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B985" s="11" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="C985" s="12"/>
       <c r="D985" s="12"/>
       <c r="E985" s="13" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="F985" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G985" s="10"/>
       <c r="H985" s="12"/>
@@ -34121,18 +34125,18 @@
     </row>
     <row r="986" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A986" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B986" s="11" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="C986" s="12"/>
       <c r="D986" s="12"/>
       <c r="E986" s="13" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="F986" s="10" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="G986" s="10"/>
       <c r="H986" s="12"/>
@@ -34141,15 +34145,15 @@
     </row>
     <row r="987" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A987" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B987" s="11" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="C987" s="12"/>
       <c r="D987" s="12"/>
       <c r="E987" s="13" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="F987" s="10"/>
       <c r="G987" s="10" t="s">
@@ -34161,26 +34165,29 @@
     </row>
     <row r="988" s="4" customFormat="1" customHeight="1" spans="1:10">
       <c r="A988" s="10" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="B988" s="11" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="C988" s="12"/>
       <c r="D988" s="12"/>
       <c r="E988" s="13" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="F988" s="10"/>
       <c r="G988" s="10"/>
       <c r="H988" s="12"/>
       <c r="I988" s="13" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="J988" s="12"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J988" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:J988">
+      <sortCondition ref="A1"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/xlsx/KV.xlsx
+++ b/xlsx/KV.xlsx
@@ -9426,7 +9426,7 @@
   <sheetFormatPr defaultColWidth="9.72972972972973" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14.4414414414414" style="5" customWidth="1"/>
-    <col min="2" max="2" width="35.7477477477477" style="6" customWidth="1"/>
+    <col min="2" max="2" width="14.1261261261261" style="6" customWidth="1"/>
     <col min="3" max="4" width="14.4414414414414" style="4" customWidth="1"/>
     <col min="5" max="5" width="23.7027027027027" style="3" customWidth="1"/>
     <col min="6" max="6" width="24.0810810810811" style="5" customWidth="1"/>
@@ -34185,7 +34185,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J988" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:J988">
+    <sortState ref="A1:J988">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
